--- a/grupos/1CM - Estadisticos 20241.xlsx
+++ b/grupos/1CM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="126">
   <si>
     <t>Materia</t>
   </si>
@@ -251,21 +251,21 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -281,94 +281,121 @@
     <t>DIAZ</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
     <t>MONTERD</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>DE LA ROSA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>GARRIDO</t>
   </si>
   <si>
     <t>JUAN</t>
   </si>
   <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>LIZBETH MARIAM</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
+    <t>MYA YAMILET</t>
+  </si>
+  <si>
+    <t>VALERIA JUNUET</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
     <t>INGRID ABIGAIL</t>
   </si>
   <si>
     <t>ISAI</t>
   </si>
   <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
     <t>CALEB SANTIAGO</t>
   </si>
   <si>
-    <t>MYA YAMILET</t>
+    <t>YOSELYN</t>
   </si>
   <si>
     <t>MARIA KAREN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
   </si>
 </sst>
 </file>
@@ -914,28 +941,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -962,25 +989,25 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>6</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE4">
         <v>5</v>
       </c>
       <c r="AF4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -1015,28 +1042,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1069,13 +1096,13 @@
         <v>8</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>6</v>
       </c>
       <c r="AD5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE5">
         <v>10</v>
@@ -1116,28 +1143,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1164,13 +1191,13 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1182,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1217,28 +1244,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1265,7 +1292,7 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1286,7 +1313,7 @@
         <v>5</v>
       </c>
       <c r="AG7">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -1318,28 +1345,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1369,7 +1396,7 @@
         <v>8</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1378,13 +1405,13 @@
         <v>7</v>
       </c>
       <c r="AD8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE8">
         <v>10</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1419,28 +1446,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1470,10 +1497,10 @@
         <v>8</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1520,28 +1547,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1571,16 +1598,16 @@
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>6</v>
       </c>
       <c r="AD10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE10">
         <v>6</v>
@@ -1621,28 +1648,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1672,22 +1699,22 @@
         <v>8</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>10</v>
       </c>
       <c r="AD11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE11">
         <v>9</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1722,28 +1749,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1770,19 +1797,19 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE12">
         <v>9</v>
@@ -1823,28 +1850,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1877,7 +1904,7 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -1889,7 +1916,7 @@
         <v>6</v>
       </c>
       <c r="AF13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1924,28 +1951,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1972,7 +1999,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1984,7 +2011,7 @@
         <v>8</v>
       </c>
       <c r="AD14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE14">
         <v>8</v>
@@ -2025,28 +2052,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2073,19 +2100,19 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC15">
         <v>10</v>
       </c>
       <c r="AD15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15">
         <v>7</v>
@@ -2126,28 +2153,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2174,10 +2201,10 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -2227,28 +2254,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2275,10 +2302,10 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2293,7 +2320,7 @@
         <v>9</v>
       </c>
       <c r="AF17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2328,28 +2355,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2388,13 +2415,13 @@
         <v>6</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE18">
         <v>6</v>
       </c>
       <c r="AF18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2429,28 +2456,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2477,10 +2504,10 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB19">
         <v>9</v>
@@ -2489,7 +2516,7 @@
         <v>10</v>
       </c>
       <c r="AD19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE19">
         <v>8</v>
@@ -2530,28 +2557,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2578,7 +2605,7 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2590,13 +2617,13 @@
         <v>10</v>
       </c>
       <c r="AD20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE20">
         <v>8</v>
       </c>
       <c r="AF20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2616,7 +2643,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -2631,28 +2658,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2682,16 +2709,16 @@
         <v>9</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE21">
         <v>9</v>
@@ -2732,28 +2759,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2780,13 +2807,13 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2833,28 +2860,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2881,19 +2908,19 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>10</v>
       </c>
       <c r="AD23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE23">
         <v>6</v>
@@ -2934,28 +2961,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2982,10 +3009,10 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>9</v>
@@ -2994,7 +3021,7 @@
         <v>7</v>
       </c>
       <c r="AD24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE24">
         <v>8</v>
@@ -3035,28 +3062,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3083,19 +3110,19 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>7</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25">
         <v>6</v>
@@ -3136,28 +3163,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3184,10 +3211,10 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>8</v>
@@ -3222,7 +3249,7 @@
         <v>10</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27">
         <v>9</v>
@@ -3237,28 +3264,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3285,19 +3312,19 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB27">
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE27">
         <v>8</v>
@@ -3338,28 +3365,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3386,10 +3413,10 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>10</v>
@@ -3439,28 +3466,28 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3487,7 +3514,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>5</v>
@@ -3540,28 +3567,28 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>-1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3588,10 +3615,10 @@
         <v>-1</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -3600,7 +3627,7 @@
         <v>10</v>
       </c>
       <c r="AD30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE30">
         <v>10</v>
@@ -3641,28 +3668,28 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3689,10 +3716,10 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>7</v>
@@ -3701,7 +3728,7 @@
         <v>6</v>
       </c>
       <c r="AD31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE31">
         <v>6</v>
@@ -3742,28 +3769,28 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
         <v>-1</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3793,7 +3820,7 @@
         <v>7</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>9</v>
@@ -3802,13 +3829,13 @@
         <v>6</v>
       </c>
       <c r="AD32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE32">
         <v>8</v>
       </c>
       <c r="AF32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3843,28 +3870,28 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3891,10 +3918,10 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB33">
         <v>10</v>
@@ -3903,7 +3930,7 @@
         <v>10</v>
       </c>
       <c r="AD33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE33">
         <v>10</v>
@@ -3944,28 +3971,28 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3992,7 +4019,7 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA34">
         <v>6</v>
@@ -4004,7 +4031,7 @@
         <v>10</v>
       </c>
       <c r="AD34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE34">
         <v>10</v>
@@ -4045,28 +4072,28 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>-1</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4093,19 +4120,19 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <v>6</v>
       </c>
       <c r="AB35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC35">
         <v>6</v>
       </c>
       <c r="AD35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE35">
         <v>7</v>
@@ -4146,28 +4173,28 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>-1</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4194,13 +4221,13 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA36">
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC36">
         <v>6</v>
@@ -4212,7 +4239,7 @@
         <v>5</v>
       </c>
       <c r="AF36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4247,28 +4274,28 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>-1</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4295,13 +4322,13 @@
         <v>-1</v>
       </c>
       <c r="Z37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC37">
         <v>6</v>
@@ -4313,7 +4340,7 @@
         <v>6</v>
       </c>
       <c r="AF37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4348,28 +4375,28 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
         <v>-1</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4402,7 +4429,7 @@
         <v>5</v>
       </c>
       <c r="AB38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC38">
         <v>10</v>
@@ -4414,7 +4441,7 @@
         <v>6</v>
       </c>
       <c r="AF38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4449,28 +4476,28 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M39">
         <v>-1</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -4497,10 +4524,10 @@
         <v>-1</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB39">
         <v>8</v>
@@ -4509,13 +4536,13 @@
         <v>8</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE39">
         <v>7</v>
       </c>
       <c r="AF39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4550,28 +4577,28 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
         <v>-1</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -4598,25 +4625,25 @@
         <v>-1</v>
       </c>
       <c r="Z40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC40">
         <v>7</v>
       </c>
       <c r="AD40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE40">
         <v>10</v>
       </c>
       <c r="AF40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -4651,28 +4678,28 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>-1</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -4699,13 +4726,13 @@
         <v>-1</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC41">
         <v>8</v>
@@ -4717,7 +4744,7 @@
         <v>9</v>
       </c>
       <c r="AF41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG41">
         <v>10</v>
@@ -4752,28 +4779,28 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>-1</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O42">
         <v>-1</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -4800,13 +4827,13 @@
         <v>-1</v>
       </c>
       <c r="Z42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA42">
         <v>6</v>
       </c>
       <c r="AB42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC42">
         <v>8</v>
@@ -4818,7 +4845,7 @@
         <v>6</v>
       </c>
       <c r="AF42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -4853,28 +4880,28 @@
         <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M43">
         <v>-1</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -4901,7 +4928,7 @@
         <v>-1</v>
       </c>
       <c r="Z43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA43">
         <v>6</v>
@@ -4954,28 +4981,28 @@
         <v>10</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M44">
         <v>-1</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O44">
         <v>-1</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
         <v>-1</v>
@@ -5002,10 +5029,10 @@
         <v>-1</v>
       </c>
       <c r="Z44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB44">
         <v>10</v>
@@ -5014,7 +5041,7 @@
         <v>10</v>
       </c>
       <c r="AD44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE44">
         <v>10</v>
@@ -5055,28 +5082,28 @@
         <v>10</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M45">
         <v>-1</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O45">
         <v>-1</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
         <v>-1</v>
@@ -5103,19 +5130,19 @@
         <v>-1</v>
       </c>
       <c r="Z45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA45">
         <v>5</v>
       </c>
       <c r="AB45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC45">
         <v>7</v>
       </c>
       <c r="AD45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE45">
         <v>6</v>
@@ -5156,28 +5183,28 @@
         <v>10</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M46">
         <v>-1</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O46">
         <v>-1</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R46">
         <v>-1</v>
@@ -5204,10 +5231,10 @@
         <v>-1</v>
       </c>
       <c r="Z46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB46">
         <v>9</v>
@@ -5257,28 +5284,28 @@
         <v>10</v>
       </c>
       <c r="J47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M47">
         <v>-1</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O47">
         <v>-1</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R47">
         <v>-1</v>
@@ -5305,19 +5332,19 @@
         <v>-1</v>
       </c>
       <c r="Z47">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC47">
         <v>10</v>
       </c>
       <c r="AD47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE47">
         <v>6</v>
@@ -5358,28 +5385,28 @@
         <v>10</v>
       </c>
       <c r="J48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M48">
         <v>-1</v>
       </c>
       <c r="N48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O48">
         <v>-1</v>
       </c>
       <c r="P48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q48">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R48">
         <v>-1</v>
@@ -5406,19 +5433,19 @@
         <v>-1</v>
       </c>
       <c r="Z48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC48">
         <v>10</v>
       </c>
       <c r="AD48">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE48">
         <v>6</v>
@@ -5459,28 +5486,28 @@
         <v>10</v>
       </c>
       <c r="J49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M49">
         <v>-1</v>
       </c>
       <c r="N49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O49">
         <v>-1</v>
       </c>
       <c r="P49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q49">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R49">
         <v>-1</v>
@@ -5507,13 +5534,13 @@
         <v>-1</v>
       </c>
       <c r="Z49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA49">
         <v>5</v>
       </c>
       <c r="AB49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC49">
         <v>6</v>
@@ -5560,28 +5587,28 @@
         <v>10</v>
       </c>
       <c r="J50">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K50">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L50">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M50">
         <v>-1</v>
       </c>
       <c r="N50">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O50">
         <v>-1</v>
       </c>
       <c r="P50">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q50">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R50">
         <v>-1</v>
@@ -5611,7 +5638,7 @@
         <v>10</v>
       </c>
       <c r="AA50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB50">
         <v>9</v>
@@ -5620,7 +5647,7 @@
         <v>6</v>
       </c>
       <c r="AD50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE50">
         <v>6</v>
@@ -5661,28 +5688,28 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K51">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L51">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M51">
         <v>-1</v>
       </c>
       <c r="N51">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O51">
         <v>-1</v>
       </c>
       <c r="P51">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q51">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R51">
         <v>-1</v>
@@ -5709,13 +5736,13 @@
         <v>-1</v>
       </c>
       <c r="Z51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA51">
         <v>5</v>
       </c>
       <c r="AB51">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC51">
         <v>10</v>
@@ -6056,7 +6083,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -6080,7 +6107,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -6130,22 +6157,22 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="L7">
-        <v>58.3</v>
+        <v>63.6</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -6154,22 +6181,22 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="T7">
-        <v>58.3</v>
+        <v>63.6</v>
       </c>
       <c r="U7">
         <v>100</v>
       </c>
       <c r="V7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W7">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -6222,7 +6249,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -6246,7 +6273,7 @@
         <v>100</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -6370,13 +6397,13 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -6394,13 +6421,13 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W10">
         <v>100</v>
       </c>
       <c r="X10">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -6438,10 +6465,10 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L11">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -6462,10 +6489,10 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T11">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -6518,13 +6545,13 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -6542,13 +6569,13 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U12">
         <v>100</v>
       </c>
       <c r="V12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W12">
         <v>100</v>
@@ -6601,13 +6628,13 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -6625,13 +6652,13 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W13">
         <v>100</v>
       </c>
       <c r="X13">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -6749,7 +6776,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -6761,7 +6788,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -6773,7 +6800,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -6785,7 +6812,7 @@
         <v>100</v>
       </c>
       <c r="X15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -6823,22 +6850,22 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
       <c r="P16">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -6847,22 +6874,22 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="W16">
         <v>100</v>
       </c>
       <c r="X16">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -7057,7 +7084,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -7069,7 +7096,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -7081,7 +7108,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -7093,7 +7120,7 @@
         <v>100</v>
       </c>
       <c r="X19">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -7146,7 +7173,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -7170,7 +7197,7 @@
         <v>100</v>
       </c>
       <c r="X20">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -7288,7 +7315,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -7312,7 +7339,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -7365,7 +7392,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -7389,7 +7416,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -7531,7 +7558,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -7555,7 +7582,7 @@
         <v>100</v>
       </c>
       <c r="X25">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -7750,7 +7777,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -7774,7 +7801,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -7839,7 +7866,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -7863,7 +7890,7 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y29">
         <v>100</v>
@@ -7981,7 +8008,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -8005,7 +8032,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -8058,7 +8085,7 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -8070,7 +8097,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -8082,7 +8109,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -8094,7 +8121,7 @@
         <v>100</v>
       </c>
       <c r="X32">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y32">
         <v>100</v>
@@ -8224,7 +8251,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -8248,7 +8275,7 @@
         <v>100</v>
       </c>
       <c r="X34">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y34">
         <v>100</v>
@@ -8286,10 +8313,10 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="L35">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -8301,7 +8328,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -8310,10 +8337,10 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="T35">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -8325,7 +8352,7 @@
         <v>100</v>
       </c>
       <c r="X35">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y35">
         <v>100</v>
@@ -8366,19 +8393,19 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M36">
         <v>100</v>
       </c>
       <c r="N36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O36">
         <v>100</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -8390,19 +8417,19 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U36">
         <v>100</v>
       </c>
       <c r="V36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W36">
         <v>100</v>
       </c>
       <c r="X36">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y36">
         <v>100</v>
@@ -8449,7 +8476,7 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O37">
         <v>100</v>
@@ -8473,7 +8500,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W37">
         <v>100</v>
@@ -8517,22 +8544,22 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L38">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M38">
         <v>100</v>
       </c>
       <c r="N38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O38">
         <v>100</v>
       </c>
       <c r="P38">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -8541,22 +8568,22 @@
         <v>100</v>
       </c>
       <c r="S38">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T38">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U38">
         <v>100</v>
       </c>
       <c r="V38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W38">
         <v>100</v>
       </c>
       <c r="X38">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y38">
         <v>100</v>
@@ -8671,7 +8698,7 @@
         <v>100</v>
       </c>
       <c r="K40">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L40">
         <v>100</v>
@@ -8695,7 +8722,7 @@
         <v>100</v>
       </c>
       <c r="S40">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T40">
         <v>100</v>
@@ -8751,19 +8778,19 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>87.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M41">
         <v>100</v>
       </c>
       <c r="N41">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O41">
         <v>100</v>
       </c>
       <c r="P41">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -8775,19 +8802,19 @@
         <v>100</v>
       </c>
       <c r="T41">
-        <v>87.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U41">
         <v>100</v>
       </c>
       <c r="V41">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W41">
         <v>100</v>
       </c>
       <c r="X41">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y41">
         <v>100</v>
@@ -8917,7 +8944,7 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="Q43">
         <v>100</v>
@@ -8941,7 +8968,7 @@
         <v>100</v>
       </c>
       <c r="X43">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="Y43">
         <v>100</v>
@@ -9213,7 +9240,7 @@
         <v>100</v>
       </c>
       <c r="L47">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M47">
         <v>100</v>
@@ -9237,7 +9264,7 @@
         <v>100</v>
       </c>
       <c r="T47">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U47">
         <v>100</v>
@@ -9290,13 +9317,13 @@
         <v>100</v>
       </c>
       <c r="L48">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M48">
         <v>100</v>
       </c>
       <c r="N48">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O48">
         <v>100</v>
@@ -9314,13 +9341,13 @@
         <v>100</v>
       </c>
       <c r="T48">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U48">
         <v>100</v>
       </c>
       <c r="V48">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W48">
         <v>100</v>
@@ -9367,19 +9394,19 @@
         <v>100</v>
       </c>
       <c r="L49">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M49">
         <v>100</v>
       </c>
       <c r="N49">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O49">
         <v>100</v>
       </c>
       <c r="P49">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q49">
         <v>100</v>
@@ -9391,19 +9418,19 @@
         <v>100</v>
       </c>
       <c r="T49">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U49">
         <v>100</v>
       </c>
       <c r="V49">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W49">
         <v>100</v>
       </c>
       <c r="X49">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y49">
         <v>100</v>
@@ -9450,13 +9477,13 @@
         <v>100</v>
       </c>
       <c r="N50">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O50">
         <v>100</v>
       </c>
       <c r="P50">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Q50">
         <v>100</v>
@@ -9474,13 +9501,13 @@
         <v>100</v>
       </c>
       <c r="V50">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W50">
         <v>100</v>
       </c>
       <c r="X50">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Y50">
         <v>100</v>
@@ -9626,19 +9653,19 @@
         <v>48</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>70.8</v>
+        <v>79.2</v>
       </c>
       <c r="G2" s="2">
-        <v>29.2</v>
+        <v>20.8</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -9658,19 +9685,19 @@
         <v>48</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>72.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G3" s="2">
-        <v>27.1</v>
+        <v>16.7</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -9702,7 +9729,7 @@
         <v>14.6</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -9713,7 +9740,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
@@ -9734,7 +9761,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -9745,7 +9772,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
@@ -9754,19 +9781,19 @@
         <v>48</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="G6" s="2">
-        <v>6.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -9777,7 +9804,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
@@ -9798,7 +9825,7 @@
         <v>2.1</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>9.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -9830,7 +9857,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9841,7 +9868,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
@@ -9862,7 +9889,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -9912,7 +9939,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9950,16 +9977,16 @@
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -9973,10 +10000,10 @@
         <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -9990,16 +10017,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920352</v>
+        <v>24330051920250</v>
       </c>
       <c r="B4" t="s">
         <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -10013,16 +10040,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920352</v>
+        <v>24330051920250</v>
       </c>
       <c r="B5" t="s">
         <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -10036,16 +10063,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920281</v>
+        <v>24330051920345</v>
       </c>
       <c r="B6" t="s">
         <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -10059,16 +10086,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920281</v>
+        <v>24330051920345</v>
       </c>
       <c r="B7" t="s">
         <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -10088,10 +10115,10 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -10111,10 +10138,10 @@
         <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -10128,16 +10155,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920351</v>
+        <v>24330051920117</v>
       </c>
       <c r="B10" t="s">
         <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -10151,16 +10178,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920351</v>
+        <v>24330051920117</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -10174,16 +10201,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920117</v>
+        <v>24330051920349</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -10197,16 +10224,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920117</v>
+        <v>24330051920349</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -10220,22 +10247,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920086</v>
+        <v>24330051920114</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -10243,22 +10270,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920086</v>
+        <v>24330051920350</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -10266,22 +10293,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920115</v>
+        <v>24330051920132</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -10289,22 +10316,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920115</v>
+        <v>24330051920352</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -10312,22 +10339,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920114</v>
+        <v>24330051920281</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -10335,22 +10362,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920350</v>
+        <v>24330051920351</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -10358,24 +10385,47 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920132</v>
+        <v>24330051920120</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920086</v>
+      </c>
+      <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20241.xlsx
+++ b/grupos/1CM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -245,6 +245,9 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -260,9 +263,6 @@
     <t>Desc Desc Desc</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -278,16 +278,10 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>GARIBAY</t>
   </si>
   <si>
-    <t>MOLINA</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>PLIEGO</t>
@@ -296,76 +290,61 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
     <t>MONTERD</t>
   </si>
   <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>MACUISTLE</t>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
     <t>LOBATO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>DE LA ROSA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
     <t>LORENZO</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>GARRIDO</t>
   </si>
   <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>ESTRELLA MONTSERRAT</t>
-  </si>
-  <si>
     <t>LIZBETH MARIAM</t>
   </si>
   <si>
-    <t>ANGEL FRANCISCO</t>
+    <t>JESUS</t>
   </si>
   <si>
     <t>MYA YAMILET</t>
@@ -374,22 +353,22 @@
     <t>VALERIA JUNUET</t>
   </si>
   <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
     <t>MARIANA</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>INGRID ABIGAIL</t>
   </si>
   <si>
     <t>ISAI</t>
   </si>
   <si>
+    <t>CRUZ ARMANDO</t>
+  </si>
+  <si>
     <t>CALEB SANTIAGO</t>
+  </si>
+  <si>
+    <t>RENATA</t>
   </si>
   <si>
     <t>YOSELYN</t>
@@ -950,13 +929,13 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -998,13 +977,13 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>8</v>
       </c>
       <c r="AE4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF4">
         <v>7</v>
@@ -1051,13 +1030,13 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -1099,7 +1078,7 @@
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD5">
         <v>8</v>
@@ -1152,13 +1131,13 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>8</v>
@@ -1200,13 +1179,13 @@
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD6">
         <v>7</v>
       </c>
       <c r="AE6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF6">
         <v>9</v>
@@ -1253,13 +1232,13 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>5</v>
@@ -1301,7 +1280,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD7">
         <v>5</v>
@@ -1354,13 +1333,13 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1402,7 +1381,7 @@
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD8">
         <v>9</v>
@@ -1455,13 +1434,13 @@
         <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>8</v>
@@ -1556,13 +1535,13 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -1604,7 +1583,7 @@
         <v>5</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD10">
         <v>6</v>
@@ -1657,13 +1636,13 @@
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -1758,13 +1737,13 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -1812,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="AE12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF12">
         <v>7</v>
@@ -1859,13 +1838,13 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>7</v>
@@ -1907,7 +1886,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD13">
         <v>5</v>
@@ -1960,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>10</v>
@@ -2008,13 +1987,13 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD14">
         <v>9</v>
       </c>
       <c r="AE14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF14">
         <v>10</v>
@@ -2061,13 +2040,13 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>10</v>
@@ -2115,7 +2094,7 @@
         <v>7</v>
       </c>
       <c r="AE15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF15">
         <v>10</v>
@@ -2162,13 +2141,13 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -2263,13 +2242,13 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -2364,13 +2343,13 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -2412,13 +2391,13 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD18">
         <v>7</v>
       </c>
       <c r="AE18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF18">
         <v>7</v>
@@ -2465,13 +2444,13 @@
         <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>10</v>
@@ -2519,7 +2498,7 @@
         <v>9</v>
       </c>
       <c r="AE19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF19">
         <v>10</v>
@@ -2566,13 +2545,13 @@
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2614,13 +2593,13 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD20">
         <v>6</v>
       </c>
       <c r="AE20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF20">
         <v>7</v>
@@ -2667,13 +2646,13 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>10</v>
@@ -2768,13 +2747,13 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>10</v>
@@ -2816,13 +2795,13 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD22">
         <v>9</v>
       </c>
       <c r="AE22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF22">
         <v>10</v>
@@ -2869,13 +2848,13 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>10</v>
@@ -2923,7 +2902,7 @@
         <v>9</v>
       </c>
       <c r="AE23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF23">
         <v>10</v>
@@ -2970,13 +2949,13 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>10</v>
@@ -3018,13 +2997,13 @@
         <v>9</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD24">
         <v>9</v>
       </c>
       <c r="AE24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF24">
         <v>10</v>
@@ -3071,13 +3050,13 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>7</v>
@@ -3125,7 +3104,7 @@
         <v>7</v>
       </c>
       <c r="AE25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF25">
         <v>7</v>
@@ -3172,13 +3151,13 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -3220,7 +3199,7 @@
         <v>8</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD26">
         <v>6</v>
@@ -3273,13 +3252,13 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>10</v>
@@ -3327,7 +3306,7 @@
         <v>10</v>
       </c>
       <c r="AE27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF27">
         <v>10</v>
@@ -3374,13 +3353,13 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
         <v>9</v>
@@ -3422,13 +3401,13 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD28">
         <v>7</v>
       </c>
       <c r="AE28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF28">
         <v>10</v>
@@ -3475,13 +3454,13 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -3523,13 +3502,13 @@
         <v>6</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD29">
         <v>5</v>
       </c>
       <c r="AE29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF29">
         <v>6</v>
@@ -3576,13 +3555,13 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>9</v>
@@ -3677,13 +3656,13 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>6</v>
@@ -3725,7 +3704,7 @@
         <v>7</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD31">
         <v>6</v>
@@ -3778,13 +3757,13 @@
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>9</v>
@@ -3826,13 +3805,13 @@
         <v>9</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD32">
         <v>8</v>
       </c>
       <c r="AE32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF32">
         <v>9</v>
@@ -3879,13 +3858,13 @@
         <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>10</v>
@@ -3933,7 +3912,7 @@
         <v>9</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF33">
         <v>10</v>
@@ -3980,13 +3959,13 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>8</v>
@@ -4028,7 +4007,7 @@
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD34">
         <v>7</v>
@@ -4081,13 +4060,13 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>6</v>
@@ -4129,7 +4108,7 @@
         <v>7</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD35">
         <v>7</v>
@@ -4182,13 +4161,13 @@
         <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>7</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>5</v>
@@ -4230,7 +4209,7 @@
         <v>7</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD36">
         <v>5</v>
@@ -4283,13 +4262,13 @@
         <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>7</v>
@@ -4331,7 +4310,7 @@
         <v>8</v>
       </c>
       <c r="AC37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD37">
         <v>5</v>
@@ -4384,13 +4363,13 @@
         <v>5</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
         <v>6</v>
@@ -4432,13 +4411,13 @@
         <v>6</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD38">
         <v>5</v>
       </c>
       <c r="AE38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF38">
         <v>7</v>
@@ -4485,13 +4464,13 @@
         <v>8</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
         <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>8</v>
@@ -4539,7 +4518,7 @@
         <v>7</v>
       </c>
       <c r="AE39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF39">
         <v>8</v>
@@ -4586,13 +4565,13 @@
         <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>8</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
         <v>9</v>
@@ -4634,13 +4613,13 @@
         <v>9</v>
       </c>
       <c r="AC40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD40">
         <v>8</v>
       </c>
       <c r="AE40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF40">
         <v>9</v>
@@ -4687,13 +4666,13 @@
         <v>5</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
         <v>6</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
         <v>6</v>
@@ -4741,7 +4720,7 @@
         <v>6</v>
       </c>
       <c r="AE41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF41">
         <v>7</v>
@@ -4788,13 +4767,13 @@
         <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N42">
         <v>6</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P42">
         <v>6</v>
@@ -4836,13 +4815,13 @@
         <v>8</v>
       </c>
       <c r="AC42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD42">
         <v>6</v>
       </c>
       <c r="AE42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF42">
         <v>8</v>
@@ -4889,13 +4868,13 @@
         <v>8</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N43">
         <v>6</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P43">
         <v>10</v>
@@ -4937,13 +4916,13 @@
         <v>9</v>
       </c>
       <c r="AC43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD43">
         <v>7</v>
       </c>
       <c r="AE43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF43">
         <v>10</v>
@@ -4990,13 +4969,13 @@
         <v>10</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N44">
         <v>9</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P44">
         <v>10</v>
@@ -5038,7 +5017,7 @@
         <v>10</v>
       </c>
       <c r="AC44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD44">
         <v>9</v>
@@ -5091,13 +5070,13 @@
         <v>7</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N45">
         <v>8</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P45">
         <v>7</v>
@@ -5139,13 +5118,13 @@
         <v>7</v>
       </c>
       <c r="AC45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD45">
         <v>6</v>
       </c>
       <c r="AE45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF45">
         <v>7</v>
@@ -5192,13 +5171,13 @@
         <v>8</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N46">
         <v>6</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P46">
         <v>8</v>
@@ -5246,7 +5225,7 @@
         <v>6</v>
       </c>
       <c r="AE46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF46">
         <v>8</v>
@@ -5293,13 +5272,13 @@
         <v>7</v>
       </c>
       <c r="M47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N47">
         <v>7</v>
       </c>
       <c r="O47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P47">
         <v>6</v>
@@ -5341,13 +5320,13 @@
         <v>6</v>
       </c>
       <c r="AC47">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD47">
         <v>7</v>
       </c>
       <c r="AE47">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF47">
         <v>5</v>
@@ -5394,13 +5373,13 @@
         <v>9</v>
       </c>
       <c r="M48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N48">
         <v>9</v>
       </c>
       <c r="O48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P48">
         <v>8</v>
@@ -5448,7 +5427,7 @@
         <v>8</v>
       </c>
       <c r="AE48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF48">
         <v>8</v>
@@ -5495,13 +5474,13 @@
         <v>5</v>
       </c>
       <c r="M49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N49">
         <v>6</v>
       </c>
       <c r="O49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P49">
         <v>5</v>
@@ -5543,7 +5522,7 @@
         <v>5</v>
       </c>
       <c r="AC49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD49">
         <v>6</v>
@@ -5596,13 +5575,13 @@
         <v>9</v>
       </c>
       <c r="M50">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P50">
         <v>8</v>
@@ -5644,13 +5623,13 @@
         <v>9</v>
       </c>
       <c r="AC50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD50">
         <v>6</v>
       </c>
       <c r="AE50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF50">
         <v>8</v>
@@ -5697,13 +5676,13 @@
         <v>5</v>
       </c>
       <c r="M51">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N51">
         <v>7</v>
       </c>
       <c r="O51">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P51">
         <v>9</v>
@@ -5745,13 +5724,13 @@
         <v>7</v>
       </c>
       <c r="AC51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD51">
         <v>5</v>
       </c>
       <c r="AE51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF51">
         <v>10</v>
@@ -6169,7 +6148,7 @@
         <v>92.5</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P7">
         <v>81.8</v>
@@ -6193,7 +6172,7 @@
         <v>92.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X7">
         <v>81.8</v>
@@ -9676,7 +9655,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
@@ -9697,7 +9676,7 @@
         <v>16.7</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -9708,7 +9687,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
@@ -9717,19 +9696,19 @@
         <v>48</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>85.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G4" s="2">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -9740,7 +9719,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
@@ -9749,19 +9728,19 @@
         <v>48</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>91.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>8.300000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -9772,7 +9751,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
@@ -9793,7 +9772,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -9804,7 +9783,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
@@ -9813,19 +9792,19 @@
         <v>48</v>
       </c>
       <c r="D7">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>97.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="G7" s="2">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="H7">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -9836,7 +9815,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>80</v>
@@ -9845,19 +9824,19 @@
         <v>48</v>
       </c>
       <c r="D8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>9.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -9939,7 +9918,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9971,22 +9950,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920129</v>
+        <v>24330051920345</v>
       </c>
       <c r="B2" t="s">
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -9994,22 +9973,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920129</v>
+        <v>24330051920345</v>
       </c>
       <c r="B3" t="s">
         <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -10017,22 +9996,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920250</v>
+        <v>24330051920132</v>
       </c>
       <c r="B4" t="s">
         <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -10040,19 +10019,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920250</v>
+        <v>24330051920132</v>
       </c>
       <c r="B5" t="s">
         <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>75</v>
@@ -10063,22 +10042,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920345</v>
+        <v>24330051920117</v>
       </c>
       <c r="B6" t="s">
         <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -10086,19 +10065,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920345</v>
+        <v>24330051920117</v>
       </c>
       <c r="B7" t="s">
         <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>76</v>
@@ -10109,16 +10088,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920347</v>
+        <v>24330051920349</v>
       </c>
       <c r="B8" t="s">
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -10132,22 +10111,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920347</v>
+        <v>24330051920349</v>
       </c>
       <c r="B9" t="s">
         <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -10155,16 +10134,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920117</v>
+        <v>24330051920350</v>
       </c>
       <c r="B10" t="s">
         <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -10178,22 +10157,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920117</v>
+        <v>24330051920352</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -10201,22 +10180,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920349</v>
+        <v>24330051920281</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -10224,19 +10203,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920349</v>
+        <v>24330051920097</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
         <v>75</v>
@@ -10247,22 +10226,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920114</v>
+        <v>24330051920351</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -10270,22 +10249,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920350</v>
+        <v>24330051920095</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -10293,19 +10272,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920132</v>
+        <v>24330051920120</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
         <v>77</v>
@@ -10316,16 +10295,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920352</v>
+        <v>24330051920086</v>
       </c>
       <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
         <v>95</v>
       </c>
-      <c r="C17" t="s">
-        <v>108</v>
-      </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -10334,98 +10313,6 @@
         <v>74</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920281</v>
-      </c>
-      <c r="B18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920351</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920120</v>
-      </c>
-      <c r="B20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920086</v>
-      </c>
-      <c r="B21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20241.xlsx
+++ b/grupos/1CM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="128">
   <si>
     <t>Materia</t>
   </si>
@@ -278,6 +278,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>GARIBAY</t>
   </si>
   <si>
@@ -311,6 +320,15 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -339,6 +357,15 @@
   </si>
   <si>
     <t>GARRIDO</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>LIZBETH MARIAM</t>
@@ -8870,7 +8897,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8902,22 +8929,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920345</v>
+        <v>24330051920129</v>
       </c>
       <c r="B2" t="s">
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8925,22 +8952,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920345</v>
+        <v>24330051920129</v>
       </c>
       <c r="B3" t="s">
         <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8948,22 +8975,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920132</v>
+        <v>24330051920129</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8971,22 +8998,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920132</v>
+        <v>24330051920250</v>
       </c>
       <c r="B5" t="s">
         <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8994,22 +9021,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920117</v>
+        <v>24330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -9017,16 +9044,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920117</v>
+        <v>24330051920250</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -9040,16 +9067,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920349</v>
+        <v>24330051920347</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -9063,22 +9090,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920349</v>
+        <v>24330051920347</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -9086,22 +9113,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920350</v>
+        <v>24330051920347</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -9109,22 +9136,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920352</v>
+        <v>24330051920345</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -9132,16 +9159,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920281</v>
+        <v>24330051920345</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -9155,22 +9182,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920097</v>
+        <v>24330051920132</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -9178,22 +9205,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920351</v>
+        <v>24330051920132</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
         <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -9201,22 +9228,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920095</v>
+        <v>24330051920117</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
         <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -9224,22 +9251,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920120</v>
+        <v>24330051920117</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -9247,16 +9274,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920086</v>
+        <v>24330051920349</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -9265,6 +9292,213 @@
         <v>74</v>
       </c>
       <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920349</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920350</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920352</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920281</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920097</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920351</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920095</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920086</v>
+      </c>
+      <c r="B26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20241.xlsx
+++ b/grupos/1CM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="130">
   <si>
     <t>Materia</t>
   </si>
@@ -254,12 +254,12 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -278,15 +278,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
     <t>GARIBAY</t>
   </si>
   <si>
@@ -320,15 +323,15 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -359,13 +362,16 @@
     <t>GARRIDO</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
     <t>JUAN</t>
-  </si>
-  <si>
-    <t>ESTRELLA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>LIZBETH MARIAM</t>
@@ -934,7 +940,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -949,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -976,7 +982,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>7</v>
@@ -1023,7 +1029,7 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -1038,13 +1044,13 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1065,7 +1071,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>8</v>
@@ -1127,13 +1133,13 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1216,13 +1222,13 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1237,7 +1243,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1305,13 +1311,13 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1394,13 +1400,13 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1483,13 +1489,13 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1510,7 +1516,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1572,13 +1578,13 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1661,13 +1667,13 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1682,13 +1688,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>10</v>
@@ -1750,13 +1756,13 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1839,13 +1845,13 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1860,7 +1866,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1928,13 +1934,13 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1949,7 +1955,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -2017,13 +2023,13 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2044,7 +2050,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2106,13 +2112,13 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2195,13 +2201,13 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2284,13 +2290,13 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2373,13 +2379,13 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2462,13 +2468,13 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2551,13 +2557,13 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2572,7 +2578,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2640,13 +2646,13 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2729,13 +2735,13 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2818,13 +2824,13 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2907,13 +2913,13 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2928,7 +2934,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2996,13 +3002,13 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -3085,13 +3091,13 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3174,13 +3180,13 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3195,7 +3201,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -3263,13 +3269,13 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3284,7 +3290,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3352,13 +3358,13 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3373,13 +3379,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>7</v>
@@ -3441,13 +3447,13 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3530,13 +3536,13 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3551,7 +3557,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3619,13 +3625,13 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3708,13 +3714,13 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3797,13 +3803,13 @@
         <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3824,7 +3830,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3886,13 +3892,13 @@
         <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3913,7 +3919,7 @@
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z37">
         <v>8</v>
@@ -3975,13 +3981,13 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -4002,7 +4008,7 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z38">
         <v>9</v>
@@ -4064,13 +4070,13 @@
         <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -4091,7 +4097,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z39">
         <v>8</v>
@@ -4153,13 +4159,13 @@
         <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q40">
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -4242,13 +4248,13 @@
         <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -4269,7 +4275,7 @@
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z41">
         <v>8</v>
@@ -4331,13 +4337,13 @@
         <v>6</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -4352,13 +4358,13 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X42">
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z42">
         <v>9</v>
@@ -4420,13 +4426,13 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q43">
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4441,7 +4447,7 @@
         <v>-1</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>6</v>
@@ -4509,13 +4515,13 @@
         <v>10</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q44">
         <v>-1</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S44">
         <v>-1</v>
@@ -4598,13 +4604,13 @@
         <v>7</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q45">
         <v>-1</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S45">
         <v>-1</v>
@@ -4625,7 +4631,7 @@
         <v>5</v>
       </c>
       <c r="Y45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z45">
         <v>8</v>
@@ -4687,13 +4693,13 @@
         <v>8</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q46">
         <v>-1</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S46">
         <v>-1</v>
@@ -4776,13 +4782,13 @@
         <v>6</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q47">
         <v>-1</v>
       </c>
       <c r="R47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S47">
         <v>-1</v>
@@ -4797,13 +4803,13 @@
         <v>-1</v>
       </c>
       <c r="W47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X47">
         <v>7</v>
       </c>
       <c r="Y47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z47">
         <v>8</v>
@@ -4865,13 +4871,13 @@
         <v>8</v>
       </c>
       <c r="P48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q48">
         <v>-1</v>
       </c>
       <c r="R48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S48">
         <v>-1</v>
@@ -4886,7 +4892,7 @@
         <v>-1</v>
       </c>
       <c r="W48">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X48">
         <v>7</v>
@@ -4954,13 +4960,13 @@
         <v>5</v>
       </c>
       <c r="P49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q49">
         <v>-1</v>
       </c>
       <c r="R49">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S49">
         <v>-1</v>
@@ -4981,7 +4987,7 @@
         <v>5</v>
       </c>
       <c r="Y49">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z49">
         <v>5</v>
@@ -5043,13 +5049,13 @@
         <v>8</v>
       </c>
       <c r="P50">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q50">
         <v>-1</v>
       </c>
       <c r="R50">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S50">
         <v>-1</v>
@@ -5132,13 +5138,13 @@
         <v>9</v>
       </c>
       <c r="P51">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q51">
         <v>-1</v>
       </c>
       <c r="R51">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S51">
         <v>-1</v>
@@ -5153,13 +5159,13 @@
         <v>-1</v>
       </c>
       <c r="W51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X51">
         <v>5</v>
       </c>
       <c r="Y51">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z51">
         <v>9</v>
@@ -5485,7 +5491,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -5553,7 +5559,7 @@
         <v>86.7</v>
       </c>
       <c r="R7">
-        <v>63.6</v>
+        <v>75</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -5825,7 +5831,7 @@
         <v>96.7</v>
       </c>
       <c r="R11">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5893,7 +5899,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -6097,7 +6103,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -6165,7 +6171,7 @@
         <v>96.7</v>
       </c>
       <c r="R16">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -6369,7 +6375,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -6573,7 +6579,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -6641,7 +6647,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -6981,7 +6987,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -7185,7 +7191,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -7253,7 +7259,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -7457,7 +7463,7 @@
         <v>90</v>
       </c>
       <c r="R35">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -7525,7 +7531,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -7661,7 +7667,7 @@
         <v>93.3</v>
       </c>
       <c r="R38">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -7865,7 +7871,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -8273,7 +8279,7 @@
         <v>100</v>
       </c>
       <c r="R47">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S47">
         <v>100</v>
@@ -8341,7 +8347,7 @@
         <v>100</v>
       </c>
       <c r="R48">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S48">
         <v>100</v>
@@ -8409,7 +8415,7 @@
         <v>100</v>
       </c>
       <c r="R49">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S49">
         <v>100</v>
@@ -8742,7 +8748,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
@@ -8751,19 +8757,19 @@
         <v>48</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>91.7</v>
+        <v>93.8</v>
       </c>
       <c r="G6" s="2">
-        <v>8.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8774,7 +8780,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
@@ -8783,19 +8789,19 @@
         <v>48</v>
       </c>
       <c r="D7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="G7" s="2">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8827,7 +8833,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8897,7 +8903,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8929,22 +8935,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920129</v>
+        <v>24330051920348</v>
       </c>
       <c r="B2" t="s">
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8952,16 +8958,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920129</v>
+        <v>24330051920348</v>
       </c>
       <c r="B3" t="s">
         <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -8975,22 +8981,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920129</v>
+        <v>24330051920348</v>
       </c>
       <c r="B4" t="s">
         <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8998,22 +9004,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920250</v>
+        <v>24330051920348</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
         <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -9030,13 +9036,13 @@
         <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -9053,13 +9059,13 @@
         <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -9067,22 +9073,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920347</v>
+        <v>24330051920250</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
         <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -9099,13 +9105,13 @@
         <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -9122,13 +9128,13 @@
         <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -9136,13 +9142,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920345</v>
+        <v>24330051920347</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
         <v>116</v>
@@ -9159,7 +9165,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920345</v>
+        <v>24330051920129</v>
       </c>
       <c r="B12" t="s">
         <v>89</v>
@@ -9168,13 +9174,13 @@
         <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -9182,22 +9188,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920132</v>
+        <v>24330051920129</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
         <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -9205,7 +9211,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920132</v>
+        <v>24330051920345</v>
       </c>
       <c r="B14" t="s">
         <v>90</v>
@@ -9214,13 +9220,13 @@
         <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -9228,22 +9234,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920117</v>
+        <v>24330051920345</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
         <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -9251,7 +9257,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920117</v>
+        <v>24330051920132</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
@@ -9260,13 +9266,13 @@
         <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -9274,22 +9280,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920349</v>
+        <v>24330051920132</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
         <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -9297,22 +9303,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920349</v>
+        <v>24330051920117</v>
       </c>
       <c r="B18" t="s">
         <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -9320,10 +9326,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920350</v>
+        <v>24330051920117</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
         <v>106</v>
@@ -9332,10 +9338,10 @@
         <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -9343,13 +9349,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920352</v>
+        <v>24330051920349</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
         <v>121</v>
@@ -9366,22 +9372,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920281</v>
+        <v>24330051920349</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -9389,22 +9395,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920097</v>
+        <v>24330051920350</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -9412,22 +9418,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920351</v>
+        <v>24330051920352</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -9435,22 +9441,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920095</v>
+        <v>24330051920281</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -9458,22 +9464,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920120</v>
+        <v>24330051920097</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -9481,24 +9487,93 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
+        <v>24330051920351</v>
+      </c>
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920095</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24330051920120</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
         <v>24330051920086</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
         <v>99</v>
       </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="D29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
         <v>74</v>
       </c>
-      <c r="G26">
+      <c r="G29">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20241.xlsx
+++ b/grupos/1CM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -248,18 +248,18 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -281,133 +281,130 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GARIBAY</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
   </si>
   <si>
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RICO</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>GARRIDO</t>
-  </si>
-  <si>
     <t>VALERIA</t>
   </si>
   <si>
+    <t>ULISES EZEQUIEL</t>
+  </si>
+  <si>
+    <t>CAROLINA DEL CARMEN</t>
+  </si>
+  <si>
     <t>ESTRELLA MONTSERRAT</t>
   </si>
   <si>
+    <t>JESUS</t>
+  </si>
+  <si>
     <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>JUAN</t>
   </si>
   <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
     <t>LIZBETH MARIAM</t>
   </si>
   <si>
-    <t>JESUS</t>
+    <t>INGRID ABIGAIL</t>
+  </si>
+  <si>
+    <t>CRUZ ARMANDO</t>
   </si>
   <si>
     <t>MYA YAMILET</t>
   </si>
   <si>
+    <t>RENATA</t>
+  </si>
+  <si>
+    <t>MARIA KAREN</t>
+  </si>
+  <si>
     <t>VALERIA JUNUET</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>INGRID ABIGAIL</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>CRUZ ARMANDO</t>
-  </si>
-  <si>
-    <t>CALEB SANTIAGO</t>
-  </si>
-  <si>
-    <t>RENATA</t>
-  </si>
-  <si>
-    <t>YOSELYN</t>
-  </si>
-  <si>
-    <t>MARIA KAREN</t>
   </si>
 </sst>
 </file>
@@ -967,13 +964,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1056,13 +1053,13 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1145,13 +1142,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1234,13 +1231,13 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1255,13 +1252,13 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1323,13 +1320,13 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1412,13 +1409,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1433,7 +1430,7 @@
         <v>8</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1501,13 +1498,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1528,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1590,13 +1587,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1679,13 +1676,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1700,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1768,13 +1765,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1789,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>6</v>
@@ -1857,13 +1854,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1946,13 +1943,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -2035,13 +2032,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2056,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>8</v>
@@ -2124,13 +2121,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2213,13 +2210,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2302,13 +2299,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2391,13 +2388,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2412,13 +2409,13 @@
         <v>9</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2480,13 +2477,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2569,13 +2566,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2658,13 +2655,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2747,13 +2744,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2836,13 +2833,13 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2857,13 +2854,13 @@
         <v>7</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB25">
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2925,13 +2922,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2946,7 +2943,7 @@
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>7</v>
@@ -3014,13 +3011,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -3103,13 +3100,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -3124,7 +3121,7 @@
         <v>8</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3192,13 +3189,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3213,7 +3210,7 @@
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>8</v>
@@ -3281,13 +3278,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3302,7 +3299,7 @@
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -3370,13 +3367,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3391,13 +3388,13 @@
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB31">
         <v>6</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3459,13 +3456,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>7</v>
@@ -3548,13 +3545,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3637,13 +3634,13 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3658,13 +3655,13 @@
         <v>8</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB34">
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3726,13 +3723,13 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>-1</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>7</v>
@@ -3815,13 +3812,13 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>6</v>
@@ -3836,13 +3833,13 @@
         <v>5</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3904,13 +3901,13 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3925,7 +3922,7 @@
         <v>8</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB37">
         <v>6</v>
@@ -3993,13 +3990,13 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>-1</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>8</v>
@@ -4014,7 +4011,7 @@
         <v>9</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>8</v>
@@ -4082,13 +4079,13 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W39">
         <v>8</v>
@@ -4103,7 +4100,7 @@
         <v>8</v>
       </c>
       <c r="AA39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB39">
         <v>8</v>
@@ -4171,13 +4168,13 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U40">
         <v>-1</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W40">
         <v>8</v>
@@ -4198,7 +4195,7 @@
         <v>9</v>
       </c>
       <c r="AC40">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4260,13 +4257,13 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U41">
         <v>-1</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>6</v>
@@ -4281,7 +4278,7 @@
         <v>8</v>
       </c>
       <c r="AA41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB41">
         <v>8</v>
@@ -4349,13 +4346,13 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>-1</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W42">
         <v>7</v>
@@ -4438,13 +4435,13 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U43">
         <v>-1</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W43">
         <v>8</v>
@@ -4459,7 +4456,7 @@
         <v>5</v>
       </c>
       <c r="AA43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB43">
         <v>7</v>
@@ -4527,13 +4524,13 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U44">
         <v>-1</v>
       </c>
       <c r="V44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W44">
         <v>8</v>
@@ -4616,13 +4613,13 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U45">
         <v>-1</v>
       </c>
       <c r="V45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W45">
         <v>8</v>
@@ -4637,13 +4634,13 @@
         <v>8</v>
       </c>
       <c r="AA45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB45">
         <v>7</v>
       </c>
       <c r="AC45">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:29">
@@ -4705,13 +4702,13 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U46">
         <v>-1</v>
       </c>
       <c r="V46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W46">
         <v>8</v>
@@ -4726,13 +4723,13 @@
         <v>10</v>
       </c>
       <c r="AA46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB46">
         <v>7</v>
       </c>
       <c r="AC46">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:29">
@@ -4794,13 +4791,13 @@
         <v>-1</v>
       </c>
       <c r="T47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U47">
         <v>-1</v>
       </c>
       <c r="V47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W47">
         <v>7</v>
@@ -4821,7 +4818,7 @@
         <v>8</v>
       </c>
       <c r="AC47">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:29">
@@ -4883,13 +4880,13 @@
         <v>-1</v>
       </c>
       <c r="T48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U48">
         <v>-1</v>
       </c>
       <c r="V48">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W48">
         <v>7</v>
@@ -4904,13 +4901,13 @@
         <v>10</v>
       </c>
       <c r="AA48">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB48">
         <v>7</v>
       </c>
       <c r="AC48">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:29">
@@ -4972,13 +4969,13 @@
         <v>-1</v>
       </c>
       <c r="T49">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U49">
         <v>-1</v>
       </c>
       <c r="V49">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W49">
         <v>6</v>
@@ -5061,13 +5058,13 @@
         <v>-1</v>
       </c>
       <c r="T50">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U50">
         <v>-1</v>
       </c>
       <c r="V50">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W50">
         <v>10</v>
@@ -5082,7 +5079,7 @@
         <v>7</v>
       </c>
       <c r="AA50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB50">
         <v>7</v>
@@ -5150,13 +5147,13 @@
         <v>-1</v>
       </c>
       <c r="T51">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U51">
         <v>-1</v>
       </c>
       <c r="V51">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W51">
         <v>6</v>
@@ -5171,13 +5168,13 @@
         <v>9</v>
       </c>
       <c r="AA51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB51">
         <v>7</v>
       </c>
       <c r="AC51">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5503,7 +5500,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -5565,13 +5562,13 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U7">
         <v>50</v>
       </c>
       <c r="V7">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -5639,7 +5636,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -5769,13 +5766,13 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U10">
         <v>100</v>
       </c>
       <c r="V10">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5905,7 +5902,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -5973,13 +5970,13 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U13">
         <v>100</v>
       </c>
       <c r="V13">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -6115,7 +6112,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -6177,13 +6174,13 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -6387,7 +6384,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -6455,7 +6452,7 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -6795,7 +6792,7 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -7067,7 +7064,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -7271,7 +7268,7 @@
         <v>100</v>
       </c>
       <c r="V32">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -7407,7 +7404,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -7475,7 +7472,7 @@
         <v>100</v>
       </c>
       <c r="V35">
-        <v>95.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -7537,13 +7534,13 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U36">
         <v>100</v>
       </c>
       <c r="V36">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -7605,7 +7602,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -7673,13 +7670,13 @@
         <v>100</v>
       </c>
       <c r="T38">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U38">
         <v>100</v>
       </c>
       <c r="V38">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -7747,7 +7744,7 @@
         <v>100</v>
       </c>
       <c r="V39">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7815,7 +7812,7 @@
         <v>100</v>
       </c>
       <c r="V40">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7877,13 +7874,13 @@
         <v>100</v>
       </c>
       <c r="T41">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U41">
         <v>100</v>
       </c>
       <c r="V41">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -8019,7 +8016,7 @@
         <v>100</v>
       </c>
       <c r="V43">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -8223,7 +8220,7 @@
         <v>100</v>
       </c>
       <c r="V46">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -8353,7 +8350,7 @@
         <v>100</v>
       </c>
       <c r="T48">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U48">
         <v>100</v>
@@ -8421,13 +8418,13 @@
         <v>100</v>
       </c>
       <c r="T49">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U49">
         <v>100</v>
       </c>
       <c r="V49">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -8489,13 +8486,13 @@
         <v>100</v>
       </c>
       <c r="T50">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U50">
         <v>100</v>
       </c>
       <c r="V50">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -8684,7 +8681,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
@@ -8693,19 +8690,19 @@
         <v>48</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>83.3</v>
+        <v>93.8</v>
       </c>
       <c r="G4" s="2">
-        <v>16.7</v>
+        <v>6.2</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8716,7 +8713,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
@@ -8725,19 +8722,19 @@
         <v>48</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>85.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="G5" s="2">
-        <v>14.6</v>
+        <v>4.2</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8748,7 +8745,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
@@ -8757,19 +8754,19 @@
         <v>48</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="G6" s="2">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8780,7 +8777,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
@@ -8789,19 +8786,19 @@
         <v>48</v>
       </c>
       <c r="D7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8903,7 +8900,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8941,7 +8938,7 @@
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
         <v>114</v>
@@ -8964,7 +8961,7 @@
         <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
         <v>114</v>
@@ -8987,7 +8984,7 @@
         <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
         <v>114</v>
@@ -8996,7 +8993,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -9010,7 +9007,7 @@
         <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
         <v>114</v>
@@ -9019,7 +9016,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -9027,7 +9024,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920250</v>
+        <v>24330051920169</v>
       </c>
       <c r="B6" t="s">
         <v>87</v>
@@ -9050,7 +9047,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920250</v>
+        <v>24330051920169</v>
       </c>
       <c r="B7" t="s">
         <v>87</v>
@@ -9062,10 +9059,10 @@
         <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -9073,7 +9070,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920250</v>
+        <v>24330051920169</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
@@ -9085,7 +9082,7 @@
         <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>76</v>
@@ -9096,7 +9093,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920347</v>
+        <v>24330051920139</v>
       </c>
       <c r="B9" t="s">
         <v>88</v>
@@ -9119,7 +9116,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920347</v>
+        <v>24330051920139</v>
       </c>
       <c r="B10" t="s">
         <v>88</v>
@@ -9142,7 +9139,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920347</v>
+        <v>24330051920139</v>
       </c>
       <c r="B11" t="s">
         <v>88</v>
@@ -9154,7 +9151,7 @@
         <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>76</v>
@@ -9165,7 +9162,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920129</v>
+        <v>24330051920250</v>
       </c>
       <c r="B12" t="s">
         <v>89</v>
@@ -9177,10 +9174,10 @@
         <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -9188,7 +9185,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920129</v>
+        <v>24330051920250</v>
       </c>
       <c r="B13" t="s">
         <v>89</v>
@@ -9200,10 +9197,10 @@
         <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -9211,7 +9208,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920345</v>
+        <v>24330051920132</v>
       </c>
       <c r="B14" t="s">
         <v>90</v>
@@ -9223,10 +9220,10 @@
         <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -9234,7 +9231,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920345</v>
+        <v>24330051920132</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
@@ -9246,10 +9243,10 @@
         <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -9257,7 +9254,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920132</v>
+        <v>24330051920347</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
@@ -9269,10 +9266,10 @@
         <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -9280,7 +9277,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920132</v>
+        <v>24330051920347</v>
       </c>
       <c r="B17" t="s">
         <v>91</v>
@@ -9303,7 +9300,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920117</v>
+        <v>24330051920129</v>
       </c>
       <c r="B18" t="s">
         <v>92</v>
@@ -9315,10 +9312,10 @@
         <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -9326,22 +9323,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920117</v>
+        <v>24330051920350</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -9349,22 +9346,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920349</v>
+        <v>24330051920345</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -9372,22 +9369,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920349</v>
+        <v>24330051920352</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -9395,22 +9392,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920350</v>
+        <v>24330051920097</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -9418,16 +9415,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920352</v>
+        <v>24330051920117</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -9441,22 +9438,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920281</v>
+        <v>24330051920095</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -9464,22 +9461,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920097</v>
+        <v>24330051920086</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -9487,93 +9484,24 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920351</v>
+        <v>24330051920349</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>24330051920095</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>24330051920120</v>
-      </c>
-      <c r="B28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>24330051920086</v>
-      </c>
-      <c r="B29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20241.xlsx
+++ b/grupos/1CM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="104">
   <si>
     <t>Materia</t>
   </si>
@@ -242,21 +242,21 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -290,39 +290,15 @@
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARIBAY</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -332,36 +308,12 @@
     <t>MARIN</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>VALERIA</t>
   </si>
   <si>
@@ -374,37 +326,10 @@
     <t>ESTRELLA MONTSERRAT</t>
   </si>
   <si>
+    <t>LIZBETH MARIAM</t>
+  </si>
+  <si>
     <t>JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>LIZBETH MARIAM</t>
-  </si>
-  <si>
-    <t>INGRID ABIGAIL</t>
-  </si>
-  <si>
-    <t>CRUZ ARMANDO</t>
-  </si>
-  <si>
-    <t>MYA YAMILET</t>
-  </si>
-  <si>
-    <t>RENATA</t>
-  </si>
-  <si>
-    <t>MARIA KAREN</t>
-  </si>
-  <si>
-    <t>VALERIA JUNUET</t>
   </si>
 </sst>
 </file>
@@ -955,19 +880,19 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -982,13 +907,13 @@
         <v>8</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>8</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -1044,19 +969,19 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1133,19 +1058,19 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1222,19 +1147,19 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1243,7 +1168,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1311,19 +1236,19 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1400,19 +1325,19 @@
         <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1489,19 +1414,19 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1516,7 +1441,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>6</v>
@@ -1578,19 +1503,19 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1605,7 +1530,7 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>8</v>
@@ -1667,19 +1592,19 @@
         <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1688,13 +1613,13 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>8</v>
@@ -1756,19 +1681,19 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1777,19 +1702,19 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -1845,19 +1770,19 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1934,19 +1859,19 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1955,19 +1880,19 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>9</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>10</v>
@@ -2023,19 +1948,19 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -2112,19 +2037,19 @@
         <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2133,13 +2058,13 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>9</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>6</v>
@@ -2201,19 +2126,19 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2228,13 +2153,13 @@
         <v>5</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2290,19 +2215,19 @@
         <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -2379,19 +2304,19 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2400,7 +2325,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2468,19 +2393,19 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2495,7 +2420,7 @@
         <v>9</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2557,19 +2482,19 @@
         <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2584,7 +2509,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA22">
         <v>9</v>
@@ -2646,19 +2571,19 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2667,7 +2592,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2679,7 +2604,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2735,19 +2660,19 @@
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2824,19 +2749,19 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2857,7 +2782,7 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -2913,19 +2838,19 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2934,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -3002,19 +2927,19 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -3023,7 +2948,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -3091,19 +3016,19 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -3112,13 +3037,13 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>8</v>
@@ -3180,19 +3105,19 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3201,19 +3126,19 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3269,19 +3194,19 @@
         <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -3296,7 +3221,7 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>9</v>
@@ -3358,19 +3283,19 @@
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3391,7 +3316,7 @@
         <v>7</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>6</v>
@@ -3447,19 +3372,19 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3480,7 +3405,7 @@
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>9</v>
@@ -3536,19 +3461,19 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3625,19 +3550,19 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3652,7 +3577,7 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA34">
         <v>6</v>
@@ -3714,19 +3639,19 @@
         <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
         <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>7</v>
@@ -3741,7 +3666,7 @@
         <v>7</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>7</v>
@@ -3803,19 +3728,19 @@
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>8</v>
@@ -3824,7 +3749,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3892,19 +3817,19 @@
         <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
         <v>10</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>9</v>
@@ -3919,13 +3844,13 @@
         <v>9</v>
       </c>
       <c r="Z37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>7</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC37">
         <v>7</v>
@@ -3981,19 +3906,19 @@
         <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
         <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T38">
         <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>6</v>
@@ -4002,19 +3927,19 @@
         <v>8</v>
       </c>
       <c r="X38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>7</v>
       </c>
       <c r="Z38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA38">
         <v>6</v>
       </c>
       <c r="AB38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC38">
         <v>7</v>
@@ -4070,19 +3995,19 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
         <v>9</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>8</v>
@@ -4097,7 +4022,7 @@
         <v>9</v>
       </c>
       <c r="Z39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA39">
         <v>8</v>
@@ -4159,19 +4084,19 @@
         <v>7</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
         <v>10</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>8</v>
@@ -4248,19 +4173,19 @@
         <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
         <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
         <v>8</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -4275,7 +4200,7 @@
         <v>8</v>
       </c>
       <c r="Z41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA41">
         <v>7</v>
@@ -4337,19 +4262,19 @@
         <v>5</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R42">
         <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T42">
         <v>6</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -4370,7 +4295,7 @@
         <v>6</v>
       </c>
       <c r="AB42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC42">
         <v>8</v>
@@ -4426,19 +4351,19 @@
         <v>7</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R43">
         <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T43">
         <v>10</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V43">
         <v>10</v>
@@ -4453,7 +4378,7 @@
         <v>9</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA43">
         <v>8</v>
@@ -4515,19 +4440,19 @@
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
         <v>10</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T44">
         <v>10</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V44">
         <v>10</v>
@@ -4604,19 +4529,19 @@
         <v>7</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R45">
         <v>10</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T45">
         <v>9</v>
       </c>
       <c r="U45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V45">
         <v>10</v>
@@ -4625,19 +4550,19 @@
         <v>8</v>
       </c>
       <c r="X45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y45">
         <v>8</v>
       </c>
       <c r="Z45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA45">
         <v>7</v>
       </c>
       <c r="AB45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC45">
         <v>8</v>
@@ -4693,19 +4618,19 @@
         <v>7</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R46">
         <v>10</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T46">
         <v>10</v>
       </c>
       <c r="U46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V46">
         <v>6</v>
@@ -4714,13 +4639,13 @@
         <v>8</v>
       </c>
       <c r="X46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y46">
         <v>9</v>
       </c>
       <c r="Z46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA46">
         <v>7</v>
@@ -4782,19 +4707,19 @@
         <v>7</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R47">
         <v>9</v>
       </c>
       <c r="S47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T47">
         <v>7</v>
       </c>
       <c r="U47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V47">
         <v>9</v>
@@ -4809,7 +4734,7 @@
         <v>7</v>
       </c>
       <c r="Z47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA47">
         <v>7</v>
@@ -4871,19 +4796,19 @@
         <v>7</v>
       </c>
       <c r="Q48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R48">
         <v>9</v>
       </c>
       <c r="S48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T48">
         <v>7</v>
       </c>
       <c r="U48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V48">
         <v>10</v>
@@ -4898,7 +4823,7 @@
         <v>9</v>
       </c>
       <c r="Z48">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA48">
         <v>7</v>
@@ -4960,19 +4885,19 @@
         <v>6</v>
       </c>
       <c r="Q49">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R49">
         <v>10</v>
       </c>
       <c r="S49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T49">
         <v>7</v>
       </c>
       <c r="U49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V49">
         <v>7</v>
@@ -4981,7 +4906,7 @@
         <v>6</v>
       </c>
       <c r="X49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y49">
         <v>7</v>
@@ -5049,19 +4974,19 @@
         <v>10</v>
       </c>
       <c r="Q50">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R50">
         <v>10</v>
       </c>
       <c r="S50">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T50">
         <v>8</v>
       </c>
       <c r="U50">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V50">
         <v>7</v>
@@ -5070,7 +4995,7 @@
         <v>10</v>
       </c>
       <c r="X50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y50">
         <v>9</v>
@@ -5082,7 +5007,7 @@
         <v>7</v>
       </c>
       <c r="AB50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC50">
         <v>8</v>
@@ -5138,19 +5063,19 @@
         <v>6</v>
       </c>
       <c r="Q51">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R51">
         <v>10</v>
       </c>
       <c r="S51">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T51">
         <v>10</v>
       </c>
       <c r="U51">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V51">
         <v>9</v>
@@ -5159,13 +5084,13 @@
         <v>6</v>
       </c>
       <c r="X51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y51">
         <v>8</v>
       </c>
       <c r="Z51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA51">
         <v>7</v>
@@ -5485,7 +5410,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R6">
         <v>95.3</v>
@@ -5553,7 +5478,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="R7">
         <v>75</v>
@@ -5565,7 +5490,7 @@
         <v>95.3</v>
       </c>
       <c r="U7">
-        <v>50</v>
+        <v>64.7</v>
       </c>
       <c r="V7">
         <v>84.40000000000001</v>
@@ -5627,7 +5552,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -5825,13 +5750,13 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R11">
         <v>95.3</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -6165,7 +6090,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="R16">
         <v>96.90000000000001</v>
@@ -6715,7 +6640,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -6777,13 +6702,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -6851,7 +6776,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -7395,7 +7320,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -7457,7 +7382,7 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R35">
         <v>95.3</v>
@@ -7599,7 +7524,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T37">
         <v>95.3</v>
@@ -7661,13 +7586,13 @@
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="R38">
         <v>95.3</v>
       </c>
       <c r="S38">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T38">
         <v>96.90000000000001</v>
@@ -7735,7 +7660,7 @@
         <v>100</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T39">
         <v>100</v>
@@ -7797,13 +7722,13 @@
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="R40">
         <v>100</v>
       </c>
       <c r="S40">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T40">
         <v>100</v>
@@ -7865,13 +7790,13 @@
         <v>100</v>
       </c>
       <c r="Q41">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R41">
         <v>90.59999999999999</v>
       </c>
       <c r="S41">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T41">
         <v>96.90000000000001</v>
@@ -8075,7 +8000,7 @@
         <v>100</v>
       </c>
       <c r="S44">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T44">
         <v>100</v>
@@ -8211,7 +8136,7 @@
         <v>100</v>
       </c>
       <c r="S46">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T46">
         <v>100</v>
@@ -8279,7 +8204,7 @@
         <v>95.3</v>
       </c>
       <c r="S47">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T47">
         <v>100</v>
@@ -8483,7 +8408,7 @@
         <v>100</v>
       </c>
       <c r="S50">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T50">
         <v>95.3</v>
@@ -8617,7 +8542,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
@@ -8626,19 +8551,19 @@
         <v>48</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>79.2</v>
+        <v>91.7</v>
       </c>
       <c r="G2" s="2">
-        <v>20.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -8649,7 +8574,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
@@ -8658,19 +8583,19 @@
         <v>48</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>83.3</v>
+        <v>95.8</v>
       </c>
       <c r="G3" s="2">
-        <v>16.7</v>
+        <v>4.2</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8681,7 +8606,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
@@ -8690,19 +8615,19 @@
         <v>48</v>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="G4" s="2">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8713,7 +8638,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
@@ -8734,7 +8659,7 @@
         <v>4.2</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8745,7 +8670,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
@@ -8754,19 +8679,19 @@
         <v>48</v>
       </c>
       <c r="D6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8900,7 +8825,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8938,16 +8863,16 @@
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8961,16 +8886,16 @@
         <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8984,13 +8909,13 @@
         <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>76</v>
@@ -9001,22 +8926,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920348</v>
+        <v>24330051920169</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -9030,13 +8955,13 @@
         <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>74</v>
@@ -9047,19 +8972,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920169</v>
+        <v>24330051920139</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>77</v>
@@ -9070,22 +8995,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920169</v>
+        <v>24330051920139</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -9093,19 +9018,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920139</v>
+        <v>24330051920250</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>74</v>
@@ -9116,22 +9041,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920139</v>
+        <v>24330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
         <v>102</v>
       </c>
-      <c r="D10" t="s">
-        <v>116</v>
-      </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -9139,369 +9064,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920139</v>
+        <v>24330051920132</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920250</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920250</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920132</v>
-      </c>
-      <c r="B14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920132</v>
-      </c>
-      <c r="B15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920347</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920347</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920129</v>
-      </c>
-      <c r="B18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920350</v>
-      </c>
-      <c r="B19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920345</v>
-      </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920352</v>
-      </c>
-      <c r="B21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920097</v>
-      </c>
-      <c r="B22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>75</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920117</v>
-      </c>
-      <c r="B23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920095</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>24330051920086</v>
-      </c>
-      <c r="B25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24330051920349</v>
-      </c>
-      <c r="B26" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>74</v>
-      </c>
-      <c r="G26">
         <v>5</v>
       </c>
     </row>
